--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_dry_and_wet_bulb_check.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_dry_and_wet_bulb_check.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -41,8 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,14 +65,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -149,7 +155,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,13 +167,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -778,16 +790,16 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>582.2</v>
+        <v>58.5</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>25</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="G4" s="11" t="n">
         <v>11.5</v>
@@ -799,19 +811,19 @@
         <v>2.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>11.7</v>
+        <v>14.7</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>1.4</v>
+      <c r="N4" s="15" t="n">
+        <v>29.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
@@ -819,25 +831,25 @@
       <c r="P4" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="R4" s="11" t="n">
+      <c r="R4" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="13" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="W4" s="13" t="n">
-        <v>1.6</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="V4" s="15" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="W4" s="11" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -855,7 +867,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>388.5</v>
+        <v>38.8</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>24</v>
@@ -869,61 +881,61 @@
       <c r="G5" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>12.1</v>
+      <c r="H5" s="15" t="n">
+        <v>12.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
+      </c>
+      <c r="L5" s="16" t="n">
+        <v>53.5</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>18.9</v>
+        <v>12.1</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>92</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Q5" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="Q5" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="R5" s="11" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="S5" s="14" t="n">
-        <v>16.7</v>
+      <c r="R5" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>52</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="V5" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V5" s="11" t="n">
         <v>20.7</v>
       </c>
-      <c r="W5" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X5" s="3" t="n">
+      <c r="W5" s="11" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X5" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="Y5" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z5" s="3" t="n">
+      <c r="Y5" s="11" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="Z5" s="11" t="n">
         <v>6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -940,22 +952,22 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>508.9</v>
+        <v>50.8</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>18.5</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>12.8</v>
+        <v>13.9</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.4</v>
@@ -964,34 +976,34 @@
         <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="M6" s="14" t="n">
-        <v>30.9</v>
+      <c r="M6" s="3" t="n">
+        <v>13.1</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>19.5</v>
+        <v>45.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>92</v>
+        <v>1.1</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="11" t="n">
         <v>23.6</v>
       </c>
-      <c r="R6" s="11" t="n">
+      <c r="R6" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>61.9</v>
+        <v>61.5</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>10.4</v>
@@ -999,17 +1011,17 @@
       <c r="V6" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1027,27 +1039,29 @@
       <c r="C7" s="3" t="n">
         <v>512.9</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="11" t="n">
         <v>23.9</v>
       </c>
-      <c r="E7" s="11" t="inlineStr"/>
-      <c r="F7" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G7" s="3" t="n">
+      <c r="E7" s="11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G7" s="11" t="n">
         <v>10.7</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>11.4</v>
+        <v>2.4</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>14.3</v>
@@ -1055,21 +1069,23 @@
       <c r="M7" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="N7" s="14" t="n">
-        <v>52.1</v>
+      <c r="N7" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>293</v>
+        <v>52.4</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q7" s="12" t="inlineStr"/>
-      <c r="R7" s="11" t="n">
-        <v>17.6</v>
+        <v>1</v>
+      </c>
+      <c r="Q7" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R7" s="16" t="n">
+        <v>1.7</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>17.9</v>
+        <v>12.4</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>59.1</v>
@@ -1077,20 +1093,20 @@
       <c r="U7" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="V7" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="W7" s="3" t="n">
+      <c r="V7" s="16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W7" s="11" t="n">
         <v>16.6</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>82.2</v>
+        <v>82.5</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>21</v>
+        <v>0.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1112,65 +1128,69 @@
         <v>21.6</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="G8" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G8" s="11" t="n">
         <v>7.7</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>6.4</v>
+        <v>11.9</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="M8" s="16" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>93</v>
+        <v>11.6</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="R8" s="11" t="n">
+      <c r="R8" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>18.1</v>
+        <v>1.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>35.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="W8" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="W8" s="11" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>800.8</v>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="X8" s="3" t="inlineStr"/>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1185,71 +1205,71 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2224.9</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>118.5</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="F9" s="9" t="n">
+        <v>222.4</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="F9" s="10" t="n">
         <v>93.09999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>20.9</v>
+        <v>30.9</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>63.1</v>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="n">
+        <v>706.4</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>260.5</v>
-      </c>
-      <c r="K9" s="9" t="n">
+        <v>260.4</v>
+      </c>
+      <c r="K9" s="10" t="n">
         <v>51.1</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="10" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="M9" s="9" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="N9" s="3" t="n">
+      <c r="M9" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="n">
+        <v>881</v>
+      </c>
+      <c r="P9" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="O9" s="3" t="n">
-        <v>1590.1</v>
-      </c>
-      <c r="P9" s="3" t="n">
+      <c r="Q9" s="10" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="R9" s="10" t="n">
         <v>114</v>
       </c>
-      <c r="R9" s="11" t="n">
+      <c r="S9" s="3" t="n">
+        <v>459</v>
+      </c>
+      <c r="T9" s="3" t="n">
         <v>88.09999999999999</v>
       </c>
-      <c r="S9" s="3" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>212.6</v>
-      </c>
       <c r="U9" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="V9" s="9" t="n">
-        <v>94</v>
-      </c>
-      <c r="W9" s="9" t="n">
-        <v>80.8</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="V9" s="10" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="W9" s="10" t="n">
+        <v>16</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>89.7</v>
+        <v>86.2</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>848.1</v>
+        <v>1312.6</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>2</v>
@@ -1268,7 +1288,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>495</v>
+        <v>44.5</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>23.7</v>
@@ -1286,58 +1306,58 @@
         <v>12.6</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L10" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L10" s="10" t="n">
         <v>14.7</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="10" t="n">
         <v>13.8</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>921.8</v>
+        <v>99.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>113.8</v>
-      </c>
-      <c r="Q10" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="R10" s="11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q10" s="11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="R10" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="S10" s="14" t="n">
-        <v>78.2</v>
+      <c r="S10" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="U10" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="U10" s="15" t="n">
+        <v>461.4</v>
+      </c>
+      <c r="V10" s="10" t="n">
         <v>10.6</v>
       </c>
-      <c r="V10" s="9" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>17.9</v>
+        <v>89.7</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>83</v>
+        <v>14410</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>3.8</v>
+        <v>19.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1353,7 +1373,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>924.2</v>
+        <v>191.8</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>22.5</v>
@@ -1364,55 +1384,55 @@
       <c r="F11" s="11" t="n">
         <v>18.1</v>
       </c>
-      <c r="G11" s="11" t="n">
-        <v>8.800000000000001</v>
+      <c r="G11" s="3" t="n">
+        <v>28.8</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>12.6</v>
+        <v>14.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>1.2</v>
+        <v>10</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>18.1</v>
+        <v>19.8</v>
+      </c>
+      <c r="N11" s="15" t="n">
+        <v>116.1</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>885</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S11" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q11" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="R11" s="16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S11" s="15" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>140649.1</v>
+      </c>
+      <c r="U11" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="T11" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" s="15" t="n">
         <v>18.8</v>
       </c>
-      <c r="W11" s="11" t="n">
+      <c r="W11" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1421,7 +1441,9 @@
       <c r="Y11" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1436,10 +1458,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>229</v>
+        <v>229.5</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>13.4</v>
@@ -1447,10 +1469,10 @@
       <c r="F12" s="11" t="n">
         <v>17.9</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="H12" s="14" t="n">
+      <c r="G12" s="11" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H12" s="15" t="n">
         <v>13</v>
       </c>
       <c r="I12" s="3" t="n">
@@ -1462,50 +1484,50 @@
       <c r="K12" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="L12" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M12" s="14" t="n">
-        <v>38.5</v>
+      <c r="L12" s="15" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>12.8</v>
+        <v>931.8</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="11" t="n">
         <v>20.5</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S12" s="3" t="n">
+      <c r="S12" s="15" t="n">
         <v>17.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>74.5</v>
+        <v>55.1</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="V12" s="13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W12" s="11" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
+      </c>
+      <c r="V12" s="16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W12" s="15" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="X12" s="15" t="n">
+        <v>18.7</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>18.4</v>
+        <v>940.5</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1536,7 +1558,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>13.1</v>
+        <v>1.3</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.4</v>
@@ -1548,21 +1570,21 @@
         <v>15.7</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>16.9</v>
+        <v>16.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>94.5</v>
+        <v>92.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q13" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q13" s="11" t="n">
         <v>15.8</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1572,24 +1594,24 @@
         <v>16.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>20.5</v>
+        <v>24.8</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>16.7</v>
+        <v>6.1</v>
+      </c>
+      <c r="V13" s="11" t="n">
+        <v>16.3</v>
       </c>
       <c r="W13" s="11" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Y13" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="Z13" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="X13" s="11" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="Y13" s="11" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z13" s="11" t="n">
         <v>2.8</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -1608,29 +1630,29 @@
       <c r="C14" s="3" t="n">
         <v>324</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E14" s="14" t="n">
+      <c r="D14" s="11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E14" s="11" t="n">
         <v>13.4</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="G14" s="3" t="n">
+      <c r="F14" s="11" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G14" s="11" t="n">
         <v>8.4</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>86.8</v>
+        <v>56.8</v>
       </c>
       <c r="L14" s="11" t="n">
         <v>14.4</v>
@@ -1647,35 +1669,35 @@
       <c r="P14" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" s="13" t="n">
-        <v>2.8</v>
+      <c r="Q14" s="11" t="n">
+        <v>21.7</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S14" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="U14" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="T14" s="3" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>7.2</v>
-      </c>
       <c r="V14" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W14" s="11" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X14" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="W14" s="15" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X14" s="15" t="n">
         <v>17.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>87.5</v>
+        <v>92</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>1.6</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1693,72 +1715,74 @@
       <c r="C15" s="3" t="n">
         <v>307.9</v>
       </c>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G15" s="3" t="n">
+      <c r="D15" s="11" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G15" s="11" t="n">
         <v>11.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>12.6</v>
+        <v>13.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>15.5</v>
+        <v>1.5</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>96.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q15" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="R15" s="11" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="S15" s="11" t="n">
+      <c r="R15" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="S15" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="T15" s="11" t="n">
+      <c r="T15" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="U15" s="11" t="n">
+      <c r="U15" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="X15" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="Y15" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W15" s="11" t="n">
+      <c r="Z15" s="3" t="n">
         <v>15.7</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Y15" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v>1.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1774,76 +1798,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1973.2</v>
-      </c>
-      <c r="D16" s="9" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="D16" s="10" t="n">
         <v>114.8</v>
       </c>
-      <c r="E16" s="9" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>96</v>
+      <c r="E16" s="10" t="n">
+        <v>674.7</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>17.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>164.4</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="L16" s="9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="L16" s="10" t="n">
         <v>73.2</v>
       </c>
-      <c r="M16" s="9" t="n">
-        <v>69.40000000000001</v>
+      <c r="M16" s="10" t="n">
+        <v>634.1</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>4.5</v>
+        <v>14.6</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Q16" s="9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="R16" s="9" t="n">
-        <v>61.4</v>
+      <c r="Q16" s="10" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="R16" s="10" t="n">
+        <v>83</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>88</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>3945.2</v>
+        <v>394.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="V16" s="9" t="n">
-        <v>84</v>
-      </c>
-      <c r="W16" s="9" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="V16" s="10" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="W16" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>428.8</v>
+        <v>1208.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1859,19 +1883,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1469.4</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>4.8</v>
+        <v>295</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>229.1</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.9</v>
+        <v>9.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.9</v>
@@ -1880,52 +1904,50 @@
         <v>1.2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="L17" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="M17" s="11" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N17" s="11" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="O17" s="11" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="P17" s="11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q17" s="9" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="R17" s="9" t="n">
+        <v>281.4</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="10" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Q17" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="R17" s="10" t="n">
         <v>16.7</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="V17" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="W17" s="10" t="n">
         <v>16.9</v>
-      </c>
-      <c r="W17" s="11" t="n">
-        <v>15.7</v>
       </c>
       <c r="X17" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>21.8</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>2</v>
@@ -1944,52 +1966,50 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>428.8</v>
+        <v>428.3</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>24.9</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H18" s="3" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="H18" s="15" t="n">
         <v>10.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3" t="n">
+      <c r="K18" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L18" s="11" t="n">
         <v>14</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>19.4</v>
+        <v>19.8</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="P18" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q18" s="13" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>17.8</v>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R18" s="16" t="n">
+        <v>47.5</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>18.1</v>
@@ -1997,23 +2017,21 @@
       <c r="T18" s="3" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="U18" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="U18" s="3" t="inlineStr"/>
       <c r="V18" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="X18" s="14" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="W18" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" s="15" t="n">
         <v>17</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>81.8</v>
+        <v>1611.4</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2031,44 +2049,44 @@
       <c r="C19" s="3" t="n">
         <v>440.6</v>
       </c>
-      <c r="D19" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="E19" s="3" t="n">
+      <c r="D19" s="11" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E19" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="11" t="n">
         <v>19.5</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>13</v>
+      <c r="G19" s="15" t="n">
+        <v>14</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="K19" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="11" t="n">
         <v>15.1</v>
       </c>
-      <c r="M19" s="13" t="n">
+      <c r="M19" s="16" t="n">
         <v>1.4</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>46.4</v>
+        <v>1.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>11.4</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" s="11" t="n">
         <v>24.9</v>
@@ -2085,20 +2103,20 @@
       <c r="U19" s="11" t="n">
         <v>14.4</v>
       </c>
-      <c r="V19" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W19" s="13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="X19" s="14" t="n">
-        <v>185.3</v>
+      <c r="V19" s="16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="X19" s="15" t="n">
+        <v>18.8</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>127.4</v>
+        <v>17.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2117,49 +2135,49 @@
         <v>153.1</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>21.9</v>
+        <v>20.7</v>
       </c>
       <c r="E20" s="11" t="n">
         <v>13.8</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>17.9</v>
+        <v>17.3</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>13</v>
+        <v>11.8</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K20" s="11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K20" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L20" s="14" t="n">
-        <v>19.4</v>
+      <c r="L20" s="11" t="n">
+        <v>15.4</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q20" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" s="13" t="n">
-        <v>87.59999999999999</v>
+        <v>9</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>18.5</v>
@@ -2168,7 +2186,7 @@
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>14.4</v>
+        <v>5.7</v>
       </c>
       <c r="V20" s="11" t="n">
         <v>17.6</v>
@@ -2211,10 +2229,10 @@
         <v>18.3</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>19.9</v>
+        <v>14.1</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>11.1</v>
@@ -2222,52 +2240,52 @@
       <c r="J21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K21" s="11" t="n">
+      <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="13" t="n">
-        <v>56.2</v>
+      <c r="L21" s="11" t="n">
+        <v>16.2</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>121.3</v>
+        <v>11.7</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>90.8</v>
+        <v>99.8</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q21" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="S21" s="3" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="T21" s="3" t="n">
+      <c r="Q21" s="11" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="R21" s="11" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="S21" s="11" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="T21" s="11" t="n">
         <v>74</v>
       </c>
-      <c r="U21" s="3" t="n">
+      <c r="U21" s="11" t="n">
         <v>6.6</v>
       </c>
-      <c r="V21" s="14" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Y21" s="3" t="n">
-        <v>880.9</v>
-      </c>
-      <c r="Z21" s="3" t="n">
+      <c r="V21" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W21" s="11" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="X21" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y21" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="Z21" s="11" t="n">
         <v>2.8</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -2290,58 +2308,58 @@
         <v>20.6</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="F22" s="11" t="n">
         <v>17.5</v>
       </c>
-      <c r="G22" s="11" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="H22" s="3" t="n">
+      <c r="G22" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H22" s="15" t="n">
         <v>13.4</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K22" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N22" s="14" t="n">
-        <v>68.90000000000001</v>
+      <c r="L22" s="11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="M22" s="16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="11" t="n">
         <v>20.4</v>
       </c>
-      <c r="R22" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="S22" s="14" t="n">
+      <c r="R22" s="11" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="S22" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="T22" s="3" t="n">
-        <v>740.8</v>
-      </c>
-      <c r="U22" s="3" t="n">
+      <c r="T22" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="U22" s="11" t="n">
         <v>6.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>16.9</v>
@@ -2350,10 +2368,10 @@
         <v>18.9</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>94.5</v>
+        <v>245</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1</v>
+        <v>10.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2369,51 +2387,49 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>477.4</v>
-      </c>
-      <c r="D23" s="9" t="n">
+        <v>177.2</v>
+      </c>
+      <c r="D23" s="10" t="n">
         <v>113.1</v>
       </c>
-      <c r="E23" s="9" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>91</v>
-      </c>
-      <c r="G23" s="13" t="n">
-        <v>265.4</v>
+      <c r="E23" s="10" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>94.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>636.4</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>80.8</v>
-      </c>
+        <v>61.2</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K23" s="11" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="L23" s="9" t="n">
-        <v>161.4</v>
-      </c>
-      <c r="M23" s="9" t="n">
-        <v>14.6</v>
+      <c r="K23" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>12.2</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>31.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.8</v>
+        <v>461.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q23" s="10" t="n">
         <v>109</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="10" t="n">
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2425,17 +2441,17 @@
       <c r="U23" s="3" t="n">
         <v>40.6</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>919.8</v>
-      </c>
-      <c r="W23" s="9" t="n">
-        <v>83.90000000000001</v>
+      <c r="V23" s="10" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="W23" s="10" t="n">
+        <v>81.09999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>942.1</v>
+        <v>91.2</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>148.8</v>
+        <v>929.5</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>13.8</v>
@@ -2457,19 +2473,19 @@
         <v>215.4</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="E24" s="11" t="n">
         <v>13.9</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="G24" s="11" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>636.4</v>
+        <v>12.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
@@ -2478,28 +2494,28 @@
         <v>1.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="L24" s="9" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="M24" s="9" t="n">
-        <v>14.4</v>
+        <v>0.5</v>
+      </c>
+      <c r="L24" s="11" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="M24" s="10" t="n">
+        <v>43.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>221.1</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="R24" s="9" t="n">
-        <v>47.8</v>
+      <c r="R24" s="10" t="n">
+        <v>17.8</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>18.1</v>
@@ -2510,14 +2526,14 @@
       <c r="U24" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" s="10" t="n">
         <v>18.3</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>87.09999999999999</v>
@@ -2539,76 +2555,72 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>130.4</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>64.31</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>18.8</v>
+        <v>28</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>10.8</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12.9</v>
+        <v>1.1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>2</v>
+        <v>10.1</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="L25" s="11" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M25" s="14" t="n">
-        <v>34.2</v>
+      <c r="L25" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M25" s="15" t="n">
+        <v>14.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>910.8</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q25" s="11" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="R25" s="13" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="S25" s="14" t="n">
-        <v>17.6</v>
+        <v>91.5</v>
+      </c>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="S25" s="15" t="n">
+        <v>11.6</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>49.5</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V25" s="11" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W25" s="11" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="X25" s="11" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="Y25" s="11" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="Z25" s="11" t="n">
-        <v>0.8</v>
+      <c r="W25" s="16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2624,16 +2636,16 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>87.8</v>
+        <v>32.6</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>23.4</v>
+        <v>22.5</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>18.9</v>
+        <v>18.1</v>
       </c>
       <c r="G26" s="11" t="n">
         <v>8.9</v>
@@ -2642,19 +2654,19 @@
         <v>12.9</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L26" s="11" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>14.9</v>
+        <v>3.9</v>
+      </c>
+      <c r="L26" s="15" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="M26" s="16" t="n">
+        <v>1.4</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>11.5</v>
@@ -2663,7 +2675,7 @@
         <v>95</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>11.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q26" s="11" t="n">
         <v>20.7</v>
@@ -2680,20 +2692,20 @@
       <c r="U26" s="11" t="n">
         <v>6.6</v>
       </c>
-      <c r="V26" s="11" t="n">
+      <c r="V26" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="W26" s="11" t="n">
+      <c r="W26" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="X26" s="11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="Y26" s="11" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="Z26" s="11" t="n">
-        <v>1.7</v>
+      <c r="X26" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2709,33 +2721,31 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="G27" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G27" s="11" t="n">
         <v>9.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="L27" s="11" t="n">
+      <c r="L27" s="15" t="n">
         <v>15.4</v>
       </c>
       <c r="M27" s="3" t="n">
@@ -2745,13 +2755,13 @@
         <v>1.6</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q27" s="11" t="n">
-        <v>20.8</v>
+        <v>1.2</v>
+      </c>
+      <c r="Q27" s="15" t="n">
+        <v>10.8</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>17.9</v>
@@ -2760,25 +2770,25 @@
         <v>19</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>71</v>
+        <v>717</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="V27" s="11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V27" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="W27" s="11" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X27" s="11" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y27" s="11" t="n">
-        <v>88.09999999999999</v>
-      </c>
-      <c r="Z27" s="11" t="n">
-        <v>2.4</v>
+      <c r="W27" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2794,40 +2804,40 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>305.9</v>
+        <v>30.5</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="E28" s="11" t="n">
         <v>13.8</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="G28" s="11" t="n">
         <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="L28" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K28" s="15" t="n">
         <v>15.4</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="L28" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M28" s="15" t="n">
         <v>14.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.4</v>
+        <v>18.5</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>95</v>
@@ -2835,14 +2845,14 @@
       <c r="P28" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q28" s="11" t="n">
-        <v>20.5</v>
+      <c r="Q28" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>17.2</v>
+        <v>41.5</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>72.8</v>
@@ -2850,20 +2860,20 @@
       <c r="U28" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V28" s="11" t="n">
+      <c r="V28" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="W28" s="11" t="n">
+      <c r="W28" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="X28" s="11" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Y28" s="11" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="Z28" s="11" t="n">
-        <v>2.2</v>
+      <c r="X28" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2882,45 +2892,45 @@
         <v>289.8</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>21.9</v>
+        <v>21.2</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>13.8</v>
+        <v>13.1</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>17.9</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>84.5</v>
+      <c r="G29" s="11" t="n">
+        <v>8.1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>23.8</v>
+        <v>13.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="L29" s="11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L29" s="15" t="n">
         <v>14.9</v>
       </c>
-      <c r="M29" s="13" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>1.6</v>
+      <c r="M29" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="N29" s="15" t="n">
+        <v>11.8</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>95</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q29" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q29" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="R29" s="3" t="n">
@@ -2930,24 +2940,24 @@
         <v>18.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>10</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="V29" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W29" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="X29" s="11" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Y29" s="11" t="n">
-        <v>85</v>
-      </c>
-      <c r="Z29" s="11" t="n">
+      <c r="V29" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="Y29" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="Z29" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -2964,73 +2974,67 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1689.9</v>
-      </c>
-      <c r="D30" s="9" t="n">
-        <v>1129.8</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="F30" s="9" t="n">
+        <v>1609.9</v>
+      </c>
+      <c r="D30" s="13" t="inlineStr"/>
+      <c r="E30" s="13" t="inlineStr"/>
+      <c r="F30" s="10" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>43.7</v>
+        <v>49.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="K30" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="K30" s="10" t="n">
         <v>38.6</v>
       </c>
-      <c r="L30" s="9" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M30" s="9" t="n">
+      <c r="L30" s="13" t="inlineStr"/>
+      <c r="M30" s="10" t="n">
         <v>11.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1.6</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>479.8</v>
+        <v>479.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q30" s="9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Q30" s="10" t="n">
         <v>105.2</v>
       </c>
-      <c r="R30" s="9" t="n">
-        <v>27.4</v>
+      <c r="R30" s="10" t="n">
+        <v>870.1</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>561.8</v>
+        <v>561.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>394.6</v>
-      </c>
-      <c r="V30" s="9" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W30" s="9" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="V30" s="10" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="W30" s="10" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>88</v>
+        <v>88.8</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>416.8</v>
+        <v>441</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>12.2</v>
@@ -3064,7 +3068,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>28.2</v>
+        <v>18.3</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>1.3</v>
@@ -3072,53 +3076,49 @@
       <c r="J31" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="L31" s="11" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="M31" s="11" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="N31" s="11" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="O31" s="11" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="P31" s="11" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="10" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="P31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" s="11" t="n">
+      <c r="Q31" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="10" t="n">
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>116.3</v>
+        <v>29.3</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="V31" s="11" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="W31" s="11" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="V31" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W31" s="10" t="n">
         <v>16.2</v>
       </c>
-      <c r="X31" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="Y31" s="11" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="Z31" s="11" t="n">
-        <v>1.7</v>
+      <c r="X31" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>214.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3134,40 +3134,38 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>481.8</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>24.9</v>
-      </c>
+        <v>23.5</v>
+      </c>
+      <c r="D32" s="14" t="inlineStr"/>
       <c r="E32" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>71.90000000000001</v>
+        <v>14.2</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>19.4</v>
+        <v>13.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="M32" s="13" t="n">
-        <v>10.51</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>16.1</v>
+        <v>16.8</v>
+      </c>
+      <c r="M32" s="11" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="N32" s="15" t="n">
+        <v>12.2</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>83</v>
@@ -3178,14 +3176,14 @@
       <c r="Q32" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="R32" s="14" t="n">
+      <c r="R32" s="15" t="n">
         <v>15.8</v>
       </c>
-      <c r="S32" s="3" t="n">
+      <c r="S32" s="15" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>2.2</v>
@@ -3194,16 +3192,16 @@
         <v>15.9</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>15.6</v>
+        <v>13.6</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>17.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>8</v>
+        <v>1482.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3219,58 +3217,58 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>422.8</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <v>6618.45</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G33" s="14" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>20.6</v>
+        <v>482.8</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>82.59999999999999</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>4.9</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>12.9</v>
+        <v>86.5</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="M33" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="M33" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="N33" s="14" t="n">
-        <v>92.40000000000001</v>
+      <c r="N33" s="15" t="n">
+        <v>84.8</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="15" t="n">
         <v>16.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>319.5</v>
+        <v>21.2</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>14.4</v>
@@ -3278,11 +3276,11 @@
       <c r="V33" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="W33" s="14" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>16.6</v>
+      <c r="W33" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="X33" s="15" t="n">
+        <v>16</v>
       </c>
       <c r="Y33" s="3" t="n">
         <v>71</v>
@@ -3304,28 +3302,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>492.8</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="E34" s="13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="G34" s="3" t="n">
+        <v>9492.799999999999</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G34" s="11" t="n">
         <v>12.6</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>18.3</v>
+      <c r="H34" s="15" t="n">
+        <v>109.5</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
@@ -3333,11 +3331,11 @@
       <c r="L34" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M34" s="13" t="n">
-        <v>91.59999999999999</v>
+      <c r="M34" s="11" t="n">
+        <v>11.6</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
@@ -3364,15 +3362,15 @@
         <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X34" s="3" t="inlineStr"/>
+        <v>13.8</v>
+      </c>
+      <c r="X34" s="15" t="n">
+        <v>16.5</v>
+      </c>
       <c r="Y34" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="Z34" s="3" t="n">
-        <v>4.2</v>
-      </c>
+      <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3387,25 +3385,25 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="E35" s="14" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E35" s="11" t="n">
         <v>13.6</v>
       </c>
-      <c r="F35" s="13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G35" s="14" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>0.4</v>
+      <c r="F35" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>279.3</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2.4</v>
+        <v>44.6</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>4</v>
@@ -3413,23 +3411,23 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="11" t="n">
-        <v>17.4</v>
+      <c r="L35" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="N35" s="11" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="O35" s="11" t="n">
-        <v>90</v>
-      </c>
-      <c r="P35" s="11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>910</v>
+      </c>
+      <c r="P35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" s="3" t="n">
-        <v>24.8</v>
+      <c r="Q35" s="16" t="n">
+        <v>94.5</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>18.8</v>
@@ -3438,24 +3436,24 @@
         <v>18.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>60</v>
+        <v>600.8</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="V35" s="11" t="n">
         <v>20.7</v>
       </c>
-      <c r="W35" s="11" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="X35" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y35" s="11" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="Z35" s="11" t="n">
+      <c r="W35" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="Z35" s="3" t="n">
         <v>6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -3472,25 +3470,25 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>498.3</v>
-      </c>
-      <c r="D36" s="11" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E36" s="11" t="n">
+        <v>9498.9</v>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="E36" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="F36" s="11" t="n">
+      <c r="F36" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="G36" s="11" t="n">
-        <v>10.3</v>
+      <c r="G36" s="16" t="n">
+        <v>41</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.4</v>
+        <v>12.7</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>4</v>
@@ -3498,14 +3496,14 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="M36" s="3" t="n">
+      <c r="L36" s="16" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="M36" s="11" t="n">
         <v>15.6</v>
       </c>
-      <c r="N36" s="14" t="n">
-        <v>81.09999999999999</v>
+      <c r="N36" s="15" t="n">
+        <v>17.4</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>91</v>
@@ -3513,20 +3511,20 @@
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="R36" s="3" t="n">
-        <v>17.9</v>
+      <c r="Q36" s="16" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="R36" s="16" t="n">
+        <v>87.90000000000001</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>55.1</v>
+        <v>52.1</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>12.8</v>
+        <v>11.2</v>
       </c>
       <c r="V36" s="11" t="n">
         <v>18.4</v>
@@ -3535,13 +3533,13 @@
         <v>15.9</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.6</v>
+        <v>16.6</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3557,76 +3555,74 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>128.1</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>92.59999999999999</v>
+        <v>2192.8</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>665.7</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>9.4</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>18.8</v>
-      </c>
+        <v>53.3</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="n">
         <v>110.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>121.8</v>
-      </c>
-      <c r="L37" s="9" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>15.6</v>
+        <v>17.6</v>
+      </c>
+      <c r="K37" s="10" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="L37" s="10" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>711.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.1</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>44930.3</v>
+        <v>44120.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q37" s="9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q37" s="10" t="n">
         <v>113.4</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="10" t="n">
         <v>81</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>24.8</v>
+        <v>84.8</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>313.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>24.8</v>
+        <v>234.8</v>
       </c>
       <c r="V37" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="W37" s="9" t="n">
+      <c r="W37" s="10" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>83.2</v>
+        <v>82</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>41252.4</v>
+        <v>206.8</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>4.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3642,40 +3638,40 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>438.6</v>
+        <v>43.8</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>18</v>
+        <v>18.9</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>18.5</v>
+        <v>10.8</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>22.3</v>
+        <v>12.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.1</v>
+        <v>12.1</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L38" s="9" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M38" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L38" s="10" t="n">
+        <v>151.3</v>
+      </c>
+      <c r="M38" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="N38" s="14" t="n">
-        <v>58.1</v>
+      <c r="N38" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>89.8</v>
@@ -3683,17 +3679,17 @@
       <c r="P38" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="10" t="n">
         <v>22.7</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>480.5</v>
+        <v>17</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>63.9</v>
+        <v>82.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>11</v>
@@ -3701,14 +3697,14 @@
       <c r="V38" s="11" t="n">
         <v>18.2</v>
       </c>
-      <c r="W38" s="9" t="n">
-        <v>15.1</v>
+      <c r="W38" s="10" t="n">
+        <v>16.1</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>21.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>4</v>
@@ -3727,76 +3723,74 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2392.3</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E39" s="14" t="n">
-        <v>23</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G39" s="14" t="n">
-        <v>11.9</v>
+        <v>39595.3</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>2.1</v>
+        <v>13</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>5.2</v>
+        <v>21.1</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="L39" s="13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N39" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="M39" s="15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q39" s="3" t="n">
-        <v>29.6</v>
+      <c r="Q39" s="16" t="n">
+        <v>22.96</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>19</v>
+        <v>28.2</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>52</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="V39" s="13" t="n">
-        <v>1.9</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="V39" s="14" t="inlineStr"/>
       <c r="W39" s="3" t="n">
-        <v>12.1</v>
+        <v>15.7</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>71</v>
+        <v>1.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3812,72 +3806,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2942.1</v>
-      </c>
-      <c r="D40" s="13" t="n">
-        <v>49.2</v>
+        <v>545.4</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F40" s="13" t="n">
-        <v>4.9</v>
+        <v>12.8</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="12" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="K40" s="15" t="n">
+        <v>11.3</v>
+      </c>
       <c r="L40" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M40" s="14" t="n">
-        <v>12</v>
+      <c r="M40" s="15" t="n">
+        <v>19.9</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0.1</v>
+        <v>16.2</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q40" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q40" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R40" s="11" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="S40" s="11" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="T40" s="11" t="n">
+      <c r="R40" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="T40" s="3" t="n">
         <v>58.8</v>
       </c>
-      <c r="U40" s="11" t="n">
+      <c r="U40" s="3" t="n">
         <v>12</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="3" t="n">
-        <v>12.1</v>
+      <c r="W40" s="15" t="n">
+        <v>16</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16.8</v>
+        <v>1.6</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3896,71 +3894,73 @@
         <v>408.4</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>13.7</v>
+        <v>23.7</v>
       </c>
       <c r="E41" s="11" t="n">
         <v>12.5</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="G41" s="11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H41" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="H41" s="15" t="n">
         <v>10.8</v>
       </c>
-      <c r="I41" s="14" t="n">
-        <v>81</v>
+      <c r="I41" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="M41" s="13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="O41" s="3" t="n">
-        <v>82</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R41" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>17.8</v>
+      <c r="Q41" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="S41" s="15" t="n">
+        <v>18</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.5</v>
+        <v>62.2</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>18.2</v>
+        <v>10.6</v>
+      </c>
+      <c r="V41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" s="16" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="X41" s="15" t="n">
+        <v>14.8</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>83</v>
+        <v>1113.8</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3976,72 +3976,76 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>340.1</v>
+        <v>331</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>18.5</v>
       </c>
-      <c r="G42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="H42" s="3" t="n">
-        <v>13.7</v>
+        <v>11.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M42" s="13" t="n">
-        <v>1.3</v>
+        <v>16.8</v>
+      </c>
+      <c r="M42" s="15" t="n">
+        <v>15.1</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>14.6</v>
+        <v>16.1</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" s="11" t="n">
+      <c r="Q42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="R42" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="S42" s="11" t="n">
+      <c r="R42" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="S42" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="T42" s="11" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="U42" s="11" t="n">
-        <v>10.4</v>
+      <c r="T42" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X42" s="3" t="inlineStr"/>
+        <v>18.1</v>
+      </c>
+      <c r="W42" s="15" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>22.2</v>
+      </c>
       <c r="Y42" s="3" t="n">
-        <v>87</v>
+        <v>16.5</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>2.6</v>
+        <v>92</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4057,74 +4061,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>537</v>
-      </c>
-      <c r="D43" s="13" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="E43" s="12" t="inlineStr"/>
+        <v>557.1</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>1.2</v>
+      </c>
       <c r="F43" s="3" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>11.7</v>
+        <v>10.8</v>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>99.59999999999999</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>1.4</v>
+        <v>28.8</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>15.1</v>
+        <v>14.2</v>
+      </c>
+      <c r="M43" s="15" t="n">
+        <v>35.4</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>81</v>
+        <v>119.4</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R43" s="13" t="n">
-        <v>1.6</v>
+      <c r="R43" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>15.6</v>
+        <v>91</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>7</v>
+        <v>122.6</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W43" s="13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>16.2</v>
+        <v>5</v>
+      </c>
+      <c r="V43" s="16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="15" t="n">
+        <v>83.59999999999999</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>81.8</v>
+        <v>12.6</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>3.7</v>
+        <v>19.1</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4140,63 +4146,77 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>223.1</v>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E44" s="11" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F44" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="G44" s="3" t="inlineStr"/>
+        <v>2983</v>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>62</v>
+      </c>
       <c r="H44" s="3" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>2.6</v>
+        <v>15.2</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>5</v>
+        <v>26.2</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N44" s="3" t="inlineStr"/>
+        <v>1.1</v>
+      </c>
+      <c r="L44" s="16" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="M44" s="16" t="n">
+        <v>82</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
       <c r="O44" s="3" t="n">
-        <v>91</v>
+        <v>549.9</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>1.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R44" s="13" t="n">
-        <v>67.09999999999999</v>
+        <v>31</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>10.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>13.9</v>
+        <v>97.5</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="14" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="W44" s="12" t="inlineStr"/>
-      <c r="X44" s="3" t="inlineStr"/>
-      <c r="Y44" s="3" t="inlineStr"/>
-      <c r="Z44" s="3" t="inlineStr"/>
+        <v>251</v>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W44" s="16" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="Y44" s="3" t="n">
+        <v>466.8</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>28.1</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4211,76 +4231,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2282</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>1981.8</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>110.8</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>62</v>
+        <v>497</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G45" s="11" t="n">
+        <v>10.3</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>20.8</v>
+        <v>11.8</v>
       </c>
       <c r="I45" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K45" s="10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L45" s="10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M45" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N45" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="J45" s="3" t="n">
-        <v>286.2</v>
-      </c>
-      <c r="K45" s="9" t="n">
-        <v>180.1</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="M45" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>31.3</v>
-      </c>
       <c r="O45" s="3" t="n">
-        <v>240.9</v>
+        <v>115.1</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="Q45" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="R45" s="9" t="n">
-        <v>10.4</v>
+      <c r="Q45" s="10" t="n">
+        <v>922.8</v>
+      </c>
+      <c r="R45" s="10" t="n">
+        <v>17.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>92.2</v>
+        <v>844.6</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>331</v>
+        <v>58.5</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="V45" s="9" t="n">
-        <v>119.8</v>
-      </c>
-      <c r="W45" s="9" t="n">
-        <v>22</v>
+        <v>11.5</v>
+      </c>
+      <c r="V45" s="10" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="W45" s="10" t="n">
+        <v>15.9</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>36</v>
+        <v>16.6</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>966.8</v>
+        <v>82.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>28.7</v>
+        <v>16.2</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4298,70 +4318,74 @@
       <c r="C46" s="3" t="n">
         <v>497</v>
       </c>
-      <c r="D46" s="11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E46" s="11" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="F46" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>10.3</v>
+      <c r="D46" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F46" s="16" t="n">
+        <v>1841.4</v>
+      </c>
+      <c r="G46" s="15" t="n">
+        <v>11.7</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>11.8</v>
+        <v>6.9</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2.5</v>
+        <v>12.8</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="9" t="n">
+      <c r="K46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L46" s="10" t="n">
         <v>14.9</v>
       </c>
-      <c r="M46" s="9" t="n">
-        <v>13.8</v>
+      <c r="M46" s="10" t="n">
+        <v>19</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>6.8</v>
+        <v>15.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>20.4</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q46" s="9" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R46" s="9" t="n">
-        <v>17.1</v>
+      <c r="Q46" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R46" s="10" t="n">
+        <v>1.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>16.2</v>
+        <v>11.6</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="9" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W46" s="9" t="n">
-        <v>15.9</v>
+        <v>11.4</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>1414</v>
+      </c>
+      <c r="V46" s="10" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="W46" s="10" t="n">
+        <v>11111115.1</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>16.6</v>
+        <v>0.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>77.8</v>
+        <v>19</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>4.8</v>
+        <v>15.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
